--- a/MA2026-projeto-pratico/MA2026-entrega-parcial/01-excel/fare_attributes.xlsx
+++ b/MA2026-projeto-pratico/MA2026-entrega-parcial/01-excel/fare_attributes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\fatecsp-MA20262-equipe-07-colossenses\MA2026-projeto-pratico\MA2026-entrega-parcial\01-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{05A8030A-FCBA-433E-BE7D-A31B0BDCF2C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD56F1D-E987-4D0A-A672-09500645CD00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{9E3EAA3C-7D2B-437C-9858-69729141D39E}"/>
   </bookViews>
@@ -65,6 +65,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -498,7 +501,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -541,13 +544,14 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Ênfase2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Ênfase3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -577,6 +581,7 @@
     <cellStyle name="Ênfase5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Ênfase6" xfId="38" builtinId="49" customBuiltin="1"/>
     <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Moeda" xfId="42" builtinId="4"/>
     <cellStyle name="Neutro" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Nota" xfId="15" builtinId="10" customBuiltin="1"/>
@@ -591,7 +596,29 @@
     <cellStyle name="Título 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -602,6 +629,21 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6388D8F1-5C20-4EC5-8775-96C9F4131D8D}" name="Fare_attributes" displayName="Fare_attributes" ref="A1:F7" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:F7" xr:uid="{6388D8F1-5C20-4EC5-8775-96C9F4131D8D}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{30DA24A5-A06E-4DD0-BE80-1E1B44C54294}" name="fare_id"/>
+    <tableColumn id="2" xr3:uid="{51E020AB-5360-4892-B013-CF9A33EEDAA3}" name="price" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{FD6D0B46-08B3-4AE0-80DF-8FB97433EF86}" name="currency_type"/>
+    <tableColumn id="4" xr3:uid="{24B6E5A6-EF62-4F23-8E97-DB5737C575E9}" name="payment_method"/>
+    <tableColumn id="5" xr3:uid="{C31A4DFD-C194-45EF-8705-D89D0131A878}" name="transfers"/>
+    <tableColumn id="6" xr3:uid="{0027E5F1-B3D7-4808-ACF6-74CFA4EC367A}" name="transfer_duration"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -926,28 +968,29 @@
   <cols>
     <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -955,8 +998,8 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1">
-        <v>5400000</v>
+      <c r="B2" s="2">
+        <v>5.4</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
@@ -972,8 +1015,8 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1">
-        <v>5400000</v>
+      <c r="B3" s="2">
+        <v>5.4</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
@@ -989,8 +1032,8 @@
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1">
-        <v>5300000</v>
+      <c r="B4" s="2">
+        <v>5.3</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
@@ -1006,8 +1049,8 @@
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1">
-        <v>9380000</v>
+      <c r="B5" s="2">
+        <v>9.3800000000000008</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
@@ -1023,8 +1066,8 @@
       <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="1">
-        <v>9380000</v>
+      <c r="B6" s="2">
+        <v>9.3800000000000008</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -1040,8 +1083,8 @@
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1">
-        <v>14680000</v>
+      <c r="B7" s="2">
+        <v>14.68</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -1055,5 +1098,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>